--- a/03_Outputs/Rio_Grande/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Rio_Grande/03_Ordenamiento/ordenamiento.xlsx
@@ -148,7 +148,7 @@
     <numFmt numFmtId="272" formatCode="#,##0.0"/>
     <numFmt numFmtId="273" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,23 +158,335 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -194,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -203,111 +515,167 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="172" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="174" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="175" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="176" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="177" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="178" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="216" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="218" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="220" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="226" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="232" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="234" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="236" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="236" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="240" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="241" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="242" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="243" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="244" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="245" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="246" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="247" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="248" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="248" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="249" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="250" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="250" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="251" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="252" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="253" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="254" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="254" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="255" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="256" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="256" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="257" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="258" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="258" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="259" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="260" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="260" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="261" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="262" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="262" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="263" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="264" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="16" numFmtId="264" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="265" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="266" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="266" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="267" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="268" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="268" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="269" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="270" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="270" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="271" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="272" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="272" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="19" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="273" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="14" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="15" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="16" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="17" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="18" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="19" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="20" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="21" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="22" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="23" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="32" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="24" fontId="32" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="33" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="25" fontId="33" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="34" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="26" fontId="34" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,12 +1004,12 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="79.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="80.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,35 +1270,35 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="137" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="137" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="137" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="137" t="inlineStr">
         <is>
           <t>Predios con uso adecuado del suelo rural</t>
         </is>
@@ -955,7 +1323,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="112">
+      <c r="E2" s="138">
         <v>0.375453513395694</v>
       </c>
     </row>
@@ -978,7 +1346,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="112">
+      <c r="E3" s="138">
         <v>0.173394303977621</v>
       </c>
     </row>
@@ -1001,7 +1369,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="112">
+      <c r="E4" s="138">
         <v>0.184548247045188</v>
       </c>
     </row>
@@ -1024,7 +1392,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="112">
+      <c r="E5" s="138">
         <v>0.116246573251323</v>
       </c>
     </row>
@@ -1047,7 +1415,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="112">
+      <c r="E6" s="138">
         <v>0.198992535145965</v>
       </c>
     </row>
@@ -1063,17 +1431,17 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="140" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="140" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1141,17 +1509,17 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="142" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1219,23 +1587,22 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="144" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="144" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1478,23 +1845,23 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="146" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="146" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="146" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1737,17 +2104,17 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="148" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1815,17 +2182,17 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="150" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1893,23 +2260,23 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="152" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="152" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="152" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2107,23 +2474,23 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="154" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="154" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="154" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2471,17 +2838,17 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="156" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="156" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2549,101 +2916,101 @@
   <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="62.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="63.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de energía (municipal)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de energía (agregado)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de acueducto (municipal)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de acueducto (agregado)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de alcantarillado (municipal)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de alcantarillado (agregado)</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de recolección de basuras (municipal)</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de recolección de basuras (agregado)</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de internet (municipal)</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de internet (agregado)</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de gas natural (municipal)</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de gas natural (agregado)</t>
         </is>
@@ -2668,50 +3035,50 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="11">
         <v>0.994133123232551</v>
       </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G2" s="12">
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" s="15">
         <v>0.753591175767125</v>
       </c>
-      <c r="H2" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" s="16">
+      <c r="H2" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" s="19">
         <v>0.577584872743644</v>
       </c>
-      <c r="J2" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" s="20">
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" s="23">
         <v>0.718389915162429</v>
       </c>
-      <c r="L2" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" s="24">
+      <c r="L2" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" s="27">
         <v>0.418644221177624</v>
       </c>
-      <c r="N2" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" s="28">
+      <c r="N2" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" s="31">
         <v>0.485652926916157</v>
       </c>
-      <c r="P2" s="30" t="inlineStr">
+      <c r="P2" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2736,50 +3103,50 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>0.996753933773046</v>
       </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" s="12">
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" s="15">
         <v>0.93507867546091</v>
       </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" s="16">
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" s="19">
         <v>0.896125880737456</v>
       </c>
-      <c r="J3" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" s="20">
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" s="23">
         <v>0.987015735092182</v>
       </c>
-      <c r="L3" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" s="24">
+      <c r="L3" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" s="27">
         <v>0.542147129679391</v>
       </c>
-      <c r="N3" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" s="28">
+      <c r="N3" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" s="31">
         <v>0.662901728724887</v>
       </c>
-      <c r="P3" s="30" t="inlineStr">
+      <c r="P3" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2804,50 +3171,50 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="11">
         <v>1</v>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G4" s="12">
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" s="15">
         <v>0.921620174285575</v>
       </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" s="16">
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" s="19">
         <v>0.84324034857115</v>
       </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" s="20">
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" s="23">
         <v>0.979983491996052</v>
       </c>
-      <c r="L4" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" s="24">
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" s="27">
         <v>0.655665940845582</v>
       </c>
-      <c r="N4" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" s="28">
+      <c r="N4" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" s="31">
         <v>0.732288748445459</v>
       </c>
-      <c r="P4" s="30" t="inlineStr">
+      <c r="P4" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2872,50 +3239,50 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="11">
         <v>1</v>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" s="12">
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" s="15">
         <v>0.864347654032105</v>
       </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" s="16">
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" s="19">
         <v>0.69901658627265</v>
       </c>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" s="20">
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" s="23">
         <v>0.978542632509524</v>
       </c>
-      <c r="L5" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" s="24">
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" s="27">
         <v>0.521781080367561</v>
       </c>
-      <c r="N5" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" s="28">
+      <c r="N5" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" s="31">
         <v>0.574963327341014</v>
       </c>
-      <c r="P5" s="30" t="inlineStr">
+      <c r="P5" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2940,262 +3307,262 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <v>1</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" s="12">
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" s="15">
         <v>0.889689827983205</v>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" s="16">
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" s="19">
         <v>0.698493837193553</v>
       </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" s="20">
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" s="23">
         <v>0.938664499525938</v>
       </c>
-      <c r="L6" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" s="24">
+      <c r="L6" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" s="27">
         <v>0.43545713124746</v>
       </c>
-      <c r="N6" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" s="28">
+      <c r="N6" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" s="31">
         <v>0.512108898821617</v>
       </c>
-      <c r="P6" s="30" t="inlineStr">
+      <c r="P6" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>PROVINCIA DEL RÍO GRANDE (promedio ponderado; sin ECV oficial)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F7" s="11">
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" s="14">
         <v>0.998979310801254</v>
       </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H7" s="15">
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H7" s="18">
         <v>0.888131416571981</v>
       </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J7" s="19">
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" s="22">
         <v>0.747867367350916</v>
       </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L7" s="23">
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" s="26">
         <v>0.94867514952269</v>
       </c>
-      <c r="M7" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N7" s="27">
+      <c r="M7" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" s="30">
         <v>0.502066083042707</v>
       </c>
-      <c r="O7" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P7" s="31">
+      <c r="O7" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" s="34">
         <v>0.581498943502871</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>SUBREGIÓN NORTE (ECV oficial)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F8" s="11">
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" s="14">
         <v>0.995995299069986</v>
       </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H8" s="15">
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H8" s="18">
         <v>0.893102677644782</v>
       </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J8" s="19">
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" s="22">
         <v>0.728573914060344</v>
       </c>
-      <c r="K8" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L8" s="23">
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" s="26">
         <v>0.884143853052556</v>
       </c>
-      <c r="M8" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N8" s="27">
+      <c r="M8" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" s="30">
         <v>0.401126509950594</v>
       </c>
-      <c r="O8" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P8" s="31">
+      <c r="O8" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" s="34">
         <v>0.562700217903468</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>DEPARTAMENTO (ANTIOQUIA) (ECV oficial)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F9" s="11">
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" s="14">
         <v>0.992586544500931</v>
       </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H9" s="15">
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H9" s="18">
         <v>0.93579635079431</v>
       </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J9" s="19">
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" s="22">
         <v>0.866893560801633</v>
       </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L9" s="23">
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" s="26">
         <v>0.944698426552535</v>
       </c>
-      <c r="M9" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N9" s="27">
+      <c r="M9" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" s="30">
         <v>0.601239746666835</v>
       </c>
-      <c r="O9" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P9" s="31">
+      <c r="O9" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" s="34">
         <v>0.66955125810138</v>
       </c>
     </row>
@@ -3211,17 +3578,17 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="158" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="158" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3289,17 +3656,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="160" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3427,17 +3794,17 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="162" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="162" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3505,17 +3872,17 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="164" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="164" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3528,7 +3895,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>494.71630629166</v>
+        <v>154.609006665583</v>
       </c>
     </row>
     <row r="3">
@@ -3538,7 +3905,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>930.985702015864</v>
+        <v>243.773051078664</v>
       </c>
     </row>
     <row r="4">
@@ -3548,7 +3915,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>878.376256281407</v>
+        <v>196.215452261307</v>
       </c>
     </row>
     <row r="5">
@@ -3558,7 +3925,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>1007.40341903352</v>
+        <v>329.654058419707</v>
       </c>
     </row>
     <row r="6">
@@ -3568,7 +3935,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>325.128536300638</v>
+        <v>89.2923673033457</v>
       </c>
     </row>
   </sheetData>
@@ -3583,17 +3950,17 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="166" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="166" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3606,7 +3973,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.287873808741374</v>
+        <v>0.340694006309148</v>
       </c>
     </row>
     <row r="3">
@@ -3616,7 +3983,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.922722092581538</v>
+        <v>0.905284974093264</v>
       </c>
     </row>
     <row r="4">
@@ -3626,7 +3993,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.540448735139001</v>
+        <v>0.507803121248499</v>
       </c>
     </row>
     <row r="5">
@@ -3636,7 +4003,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.330616426153572</v>
+        <v>0.812984891792568</v>
       </c>
     </row>
     <row r="6">
@@ -3646,7 +4013,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.72375859434683</v>
+        <v>0.731293463143254</v>
       </c>
     </row>
   </sheetData>
@@ -3661,29 +4028,29 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="168" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="168" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="168" t="inlineStr">
         <is>
           <t>Déficit cuantitativo de vivienda</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="168" t="inlineStr">
         <is>
           <t>Déficit cualitativo de vivienda</t>
         </is>
@@ -3781,47 +4148,47 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="68.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="69.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="36" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="36" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="36" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="36" t="inlineStr">
         <is>
           <t>Km de vía primaria por km² del municipio</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="36" t="inlineStr">
         <is>
           <t>Km de vía secundaria por km² del municipio</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="36" t="inlineStr">
         <is>
           <t>Km de vía terciaria por km² del municipio</t>
         </is>
@@ -3846,13 +4213,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="38">
         <v>0</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="40">
         <v>0.163548335624974</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="42">
         <v>0.353954380947535</v>
       </c>
     </row>
@@ -3875,13 +4242,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="38">
         <v>0.0898779116775104</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="40">
         <v>0.0935551324220347</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="42">
         <v>0.662371703982316</v>
       </c>
     </row>
@@ -3904,13 +4271,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="38">
         <v>0</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="40">
         <v>0.186632865719644</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="42">
         <v>0.411591347790453</v>
       </c>
     </row>
@@ -3933,13 +4300,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="38">
         <v>0</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="40">
         <v>0.195859464633244</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="42">
         <v>0.381989669748716</v>
       </c>
     </row>
@@ -3962,44 +4329,44 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="38">
         <v>0.0430216983878975</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="40">
         <v>0.175097394160525</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="42">
         <v>0.275879941278116</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA DEL RÍO GRANDE (por área del municipio)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="33">
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="39">
         <v>0.0308320544694068</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="41">
         <v>0.167904817924187</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="43">
         <v>0.361586860431411</v>
       </c>
     </row>
@@ -4015,47 +4382,47 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="59.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="60.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>Km de vía primaria por cada 1.000 hab.</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Km de vía secundaria por cada 1.000 hab.</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>Km de vía terciaria por cada 1.000 hab.</t>
         </is>
@@ -4080,13 +4447,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="47">
         <v>0</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="49">
         <v>7.62041497108021</v>
       </c>
-      <c r="G2" s="42">
+      <c r="G2" s="51">
         <v>16.4922452640365</v>
       </c>
     </row>
@@ -4109,13 +4476,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="47">
         <v>0.904745481233726</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="49">
         <v>0.941761793584692</v>
       </c>
-      <c r="G3" s="42">
+      <c r="G3" s="51">
         <v>6.66768725363072</v>
       </c>
     </row>
@@ -4138,13 +4505,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="47">
         <v>0</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="49">
         <v>3.33633810712028</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="51">
         <v>7.35780320845038</v>
       </c>
     </row>
@@ -4167,13 +4534,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="47">
         <v>0</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="49">
         <v>1.84843590215059</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="51">
         <v>3.6050513113387</v>
       </c>
     </row>
@@ -4196,44 +4563,44 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="47">
         <v>0.960172206251683</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="49">
         <v>3.90788038501352</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="51">
         <v>6.15717793122065</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA DEL RÍO GRANDE (por población)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="39">
+      <c r="C7" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="48">
         <v>0.551154766137911</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="50">
         <v>3.00001603166427</v>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="52">
         <v>6.46018876684406</v>
       </c>
     </row>
@@ -4249,71 +4616,71 @@
   <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="54" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral total ($)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral urbano ($)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral rural ($)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="54" t="inlineStr">
         <is>
           <t>Proporción del avalúo catastral urbano sobre el total</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="54" t="inlineStr">
         <is>
           <t>Proporción del avalúo catastral rural sobre el total</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Estado del catastro rural</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="54" t="inlineStr">
         <is>
           <t>Estado del catastro urbano</t>
         </is>
@@ -4338,19 +4705,19 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="56">
         <v>299811796000</v>
       </c>
-      <c r="F2" s="46">
+      <c r="F2" s="58">
         <v>74273917000</v>
       </c>
-      <c r="G2" s="48">
+      <c r="G2" s="60">
         <v>225537879000</v>
       </c>
-      <c r="H2" s="50">
+      <c r="H2" s="62">
         <v>0.247735139147093</v>
       </c>
-      <c r="I2" s="52">
+      <c r="I2" s="64">
         <v>0.752264860852907</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -4383,19 +4750,19 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="56">
         <v>1329360431037</v>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="58">
         <v>782628723004</v>
       </c>
-      <c r="G3" s="48">
+      <c r="G3" s="60">
         <v>546731708033</v>
       </c>
-      <c r="H3" s="50">
+      <c r="H3" s="62">
         <v>0.588725754680009</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3" s="64">
         <v>0.411274245319991</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -4428,19 +4795,19 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="56">
         <v>1025847461018</v>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="58">
         <v>478077568002</v>
       </c>
-      <c r="G4" s="48">
+      <c r="G4" s="60">
         <v>547769893016</v>
       </c>
-      <c r="H4" s="50">
+      <c r="H4" s="62">
         <v>0.46603182848216</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4" s="64">
         <v>0.53396817151784</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -4473,19 +4840,19 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="56">
         <v>2685633990060</v>
       </c>
-      <c r="F5" s="46">
+      <c r="F5" s="58">
         <v>1029485010000</v>
       </c>
-      <c r="G5" s="48">
+      <c r="G5" s="60">
         <v>1656148980060</v>
       </c>
-      <c r="H5" s="50">
+      <c r="H5" s="62">
         <v>0.383330347251451</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="64">
         <v>0.616669652748549</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -4518,19 +4885,19 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="56">
         <v>2750863881332</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="58">
         <v>1419308047036</v>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="60">
         <v>1331555834296</v>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="62">
         <v>0.515949937278887</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="64">
         <v>0.484050062721113</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -4545,47 +4912,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="45">
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="57">
         <v>8091517559447</v>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="59">
         <v>3783773265042</v>
       </c>
-      <c r="G7" s="49">
+      <c r="G7" s="61">
         <v>4307744294405</v>
       </c>
-      <c r="H7" s="51">
+      <c r="H7" s="63">
         <v>0.467622202787458</v>
       </c>
-      <c r="I7" s="53">
+      <c r="I7" s="65">
         <v>0.532377797212542</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="J7" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4603,100 +4970,100 @@
   <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="64.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="15" max="16" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="65.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="15" max="16" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="67" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="67" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="67" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="67" t="inlineStr">
         <is>
           <t>IMCA total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="67" t="inlineStr">
         <is>
           <t>IMCA adopción TIC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="67" t="inlineStr">
         <is>
           <t>IMCA capacidades</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="67" t="inlineStr">
         <is>
           <t>IMCA dinamismo de los negocios</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="67" t="inlineStr">
         <is>
           <t>IMCA infraestructura</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="67" t="inlineStr">
         <is>
           <t>IMCA innovación</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="67" t="inlineStr">
         <is>
           <t>IMCA instituciones</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="67" t="inlineStr">
         <is>
           <t>IMCA mercado de bienes</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="67" t="inlineStr">
         <is>
           <t>IMCA mercado laboral</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="67" t="inlineStr">
         <is>
           <t>IMCA salud</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="67" t="inlineStr">
         <is>
           <t>IMCA sistema financiero</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="67" t="inlineStr">
         <is>
           <t>IMCA tamaño del mercado</t>
         </is>
@@ -4721,40 +5088,40 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="54">
+      <c r="E2" s="69">
         <v>31.9201087157624</v>
       </c>
-      <c r="F2" s="56">
+      <c r="F2" s="71">
         <v>7.91483880690836</v>
       </c>
-      <c r="G2" s="58">
+      <c r="G2" s="73">
         <v>48.7828464030074</v>
       </c>
-      <c r="H2" s="60">
+      <c r="H2" s="75">
         <v>63.704227773906</v>
       </c>
-      <c r="I2" s="62">
+      <c r="I2" s="77">
         <v>47.8221011040239</v>
       </c>
-      <c r="J2" s="64">
+      <c r="J2" s="79">
         <v>0</v>
       </c>
-      <c r="K2" s="66">
+      <c r="K2" s="81">
         <v>57.6828342826124</v>
       </c>
-      <c r="L2" s="68">
+      <c r="L2" s="83">
         <v>4.07444875883663</v>
       </c>
-      <c r="M2" s="70">
+      <c r="M2" s="85">
         <v>36.711359322978</v>
       </c>
-      <c r="N2" s="72">
+      <c r="N2" s="87">
         <v>51.5085862392968</v>
       </c>
-      <c r="O2" s="74">
+      <c r="O2" s="89">
         <v>8.89777632676171</v>
       </c>
-      <c r="P2" s="76">
+      <c r="P2" s="91">
         <v>24.0221768550555</v>
       </c>
     </row>
@@ -4777,40 +5144,40 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="54">
+      <c r="E3" s="69">
         <v>40.1170584382133</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="71">
         <v>21.9375251540601</v>
       </c>
-      <c r="G3" s="58">
+      <c r="G3" s="73">
         <v>46.6541049516201</v>
       </c>
-      <c r="H3" s="60">
+      <c r="H3" s="75">
         <v>64.7149227887857</v>
       </c>
-      <c r="I3" s="62">
+      <c r="I3" s="77">
         <v>56.6184712568275</v>
       </c>
-      <c r="J3" s="64">
+      <c r="J3" s="79">
         <v>0</v>
       </c>
-      <c r="K3" s="66">
+      <c r="K3" s="81">
         <v>56.1126258218043</v>
       </c>
-      <c r="L3" s="68">
+      <c r="L3" s="83">
         <v>25.1362068990059</v>
       </c>
-      <c r="M3" s="70">
+      <c r="M3" s="85">
         <v>56.876514105875</v>
       </c>
-      <c r="N3" s="72">
+      <c r="N3" s="87">
         <v>51.8410272144023</v>
       </c>
-      <c r="O3" s="74">
+      <c r="O3" s="89">
         <v>37.8910080919661</v>
       </c>
-      <c r="P3" s="76">
+      <c r="P3" s="91">
         <v>23.5052365359999</v>
       </c>
     </row>
@@ -4833,40 +5200,40 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="69">
         <v>35.346566991739</v>
       </c>
-      <c r="F4" s="56">
+      <c r="F4" s="71">
         <v>12.0085775643987</v>
       </c>
-      <c r="G4" s="58">
+      <c r="G4" s="73">
         <v>46.286369716768</v>
       </c>
-      <c r="H4" s="60">
+      <c r="H4" s="75">
         <v>62.3740030299918</v>
       </c>
-      <c r="I4" s="62">
+      <c r="I4" s="77">
         <v>56.2924214921809</v>
       </c>
-      <c r="J4" s="64">
+      <c r="J4" s="79">
         <v>0</v>
       </c>
-      <c r="K4" s="66">
+      <c r="K4" s="81">
         <v>56.2470873607123</v>
       </c>
-      <c r="L4" s="68">
+      <c r="L4" s="83">
         <v>19.3476158462836</v>
       </c>
-      <c r="M4" s="70">
+      <c r="M4" s="85">
         <v>37.2903105244408</v>
       </c>
-      <c r="N4" s="72">
+      <c r="N4" s="87">
         <v>46.4532068220272</v>
       </c>
-      <c r="O4" s="74">
+      <c r="O4" s="89">
         <v>25.0722538089193</v>
       </c>
-      <c r="P4" s="76">
+      <c r="P4" s="91">
         <v>27.4403907434065</v>
       </c>
     </row>
@@ -4889,40 +5256,40 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="69">
         <v>40.3317696308486</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="71">
         <v>16.5244422800332</v>
       </c>
-      <c r="G5" s="58">
+      <c r="G5" s="73">
         <v>66.4931293751286</v>
       </c>
-      <c r="H5" s="60">
+      <c r="H5" s="75">
         <v>65.8230672099844</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="77">
         <v>58.1667823849133</v>
       </c>
-      <c r="J5" s="64">
+      <c r="J5" s="79">
         <v>0</v>
       </c>
-      <c r="K5" s="66">
+      <c r="K5" s="81">
         <v>56.8455338661176</v>
       </c>
-      <c r="L5" s="68">
+      <c r="L5" s="83">
         <v>20.6885771754825</v>
       </c>
-      <c r="M5" s="70">
+      <c r="M5" s="85">
         <v>48.5803670005071</v>
       </c>
-      <c r="N5" s="72">
+      <c r="N5" s="87">
         <v>47.8145890095089</v>
       </c>
-      <c r="O5" s="74">
+      <c r="O5" s="89">
         <v>36.3856144791017</v>
       </c>
-      <c r="P5" s="76">
+      <c r="P5" s="91">
         <v>26.3273631585573</v>
       </c>
     </row>
@@ -4945,156 +5312,156 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="69">
         <v>37.8825296899913</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="71">
         <v>15.5624913008017</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="73">
         <v>55.6130909273824</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="75">
         <v>62.3538460523115</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="77">
         <v>56.1060197213819</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="79">
         <v>0</v>
       </c>
-      <c r="K6" s="66">
+      <c r="K6" s="81">
         <v>51.3455960295751</v>
       </c>
-      <c r="L6" s="68">
+      <c r="L6" s="83">
         <v>17.7932891368288</v>
       </c>
-      <c r="M6" s="70">
+      <c r="M6" s="85">
         <v>51.7542480585983</v>
       </c>
-      <c r="N6" s="72">
+      <c r="N6" s="87">
         <v>49.7407462354588</v>
       </c>
-      <c r="O6" s="74">
+      <c r="O6" s="89">
         <v>33.6479681034851</v>
       </c>
-      <c r="P6" s="76">
+      <c r="P6" s="91">
         <v>22.7905310240804</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="68" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA DEL RÍO GRANDE (por población 2022)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="55">
+      <c r="C7" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="70">
         <v>38.2222443669408</v>
       </c>
-      <c r="F7" s="57">
+      <c r="F7" s="72">
         <v>16.1597735073615</v>
       </c>
-      <c r="G7" s="59">
+      <c r="G7" s="74">
         <v>54.8040339385425</v>
       </c>
-      <c r="H7" s="61">
+      <c r="H7" s="76">
         <v>63.7212711918489</v>
       </c>
-      <c r="I7" s="63">
+      <c r="I7" s="78">
         <v>56.1874697478544</v>
       </c>
-      <c r="J7" s="65">
+      <c r="J7" s="80">
         <v>0</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="82">
         <v>54.5628102462341</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="84">
         <v>19.2588579620949</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="86">
         <v>49.3747457624171</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="88">
         <v>49.4348152753934</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="90">
         <v>32.5542078840161</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="92">
         <v>24.3867025205861</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="68" t="inlineStr">
         <is>
           <t>SUBREGIÓN NORTE (IMCA oficial de subregión)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="68" t="inlineStr">
         <is>
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="55">
+      <c r="D8" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="70">
         <v>32.4797103611666</v>
       </c>
-      <c r="F8" s="57">
+      <c r="F8" s="72">
         <v>9.28015207353694</v>
       </c>
-      <c r="G8" s="59">
+      <c r="G8" s="74">
         <v>41.9074122002197</v>
       </c>
-      <c r="H8" s="61">
+      <c r="H8" s="76">
         <v>58.4405416967164</v>
       </c>
-      <c r="I8" s="63">
+      <c r="I8" s="78">
         <v>50.6088657345118</v>
       </c>
-      <c r="J8" s="65">
+      <c r="J8" s="80">
         <v>0</v>
       </c>
-      <c r="K8" s="67">
+      <c r="K8" s="82">
         <v>52.6170318351737</v>
       </c>
-      <c r="L8" s="69">
+      <c r="L8" s="84">
         <v>8.22485538099614</v>
       </c>
-      <c r="M8" s="71">
+      <c r="M8" s="86">
         <v>43.6804795248635</v>
       </c>
-      <c r="N8" s="73">
+      <c r="N8" s="88">
         <v>47.6738144536003</v>
       </c>
-      <c r="O8" s="75">
+      <c r="O8" s="90">
         <v>23.3042940081032</v>
       </c>
-      <c r="P8" s="77">
+      <c r="P8" s="92">
         <v>21.5393670651105</v>
       </c>
     </row>
@@ -5110,101 +5477,101 @@
   <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="64.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="65.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="94" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="94" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="94" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="94" t="inlineStr">
         <is>
           <t>Índice de Gobierno Digital</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="94" t="inlineStr">
         <is>
           <t>Gobernanza</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="94" t="inlineStr">
         <is>
           <t>Innovación Pública Digital</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="94" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="94" t="inlineStr">
         <is>
           <t>Seguridad y Privacidad de la Información</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="94" t="inlineStr">
         <is>
           <t>Servicios Ciudadanos Digitales</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="94" t="inlineStr">
         <is>
           <t>Cultura y Apropiación</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="94" t="inlineStr">
         <is>
           <t>Servicios y Procesos Inteligentes</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="94" t="inlineStr">
         <is>
           <t>Estado Abierto</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="94" t="inlineStr">
         <is>
           <t>Decisiones basadas en datos</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="94" t="inlineStr">
         <is>
           <t>Proyectos de Transformación Digital</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="94" t="inlineStr">
         <is>
           <t>Estrategias de Ciudades y Territorios Inteligentes</t>
         </is>
@@ -5229,42 +5596,42 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="78">
+      <c r="E2" s="96">
         <v>68.3</v>
       </c>
-      <c r="F2" s="80">
+      <c r="F2" s="98">
         <v>41.75</v>
       </c>
-      <c r="G2" s="82">
+      <c r="G2" s="100">
         <v>0</v>
       </c>
-      <c r="H2" s="84">
+      <c r="H2" s="102">
         <v>0</v>
       </c>
-      <c r="I2" s="86">
+      <c r="I2" s="104">
         <v>33.33</v>
       </c>
-      <c r="J2" s="88">
+      <c r="J2" s="106">
         <v>75</v>
       </c>
-      <c r="K2" s="90">
+      <c r="K2" s="108">
         <v>76</v>
       </c>
-      <c r="L2" s="92">
+      <c r="L2" s="110">
         <v>44.44</v>
       </c>
-      <c r="M2" s="94">
+      <c r="M2" s="112">
         <v>92</v>
       </c>
-      <c r="N2" s="96">
+      <c r="N2" s="114">
         <v>28</v>
       </c>
-      <c r="O2" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" s="100" t="inlineStr">
+      <c r="O2" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5289,42 +5656,42 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="78">
+      <c r="E3" s="96">
         <v>66.93</v>
       </c>
-      <c r="F3" s="80">
+      <c r="F3" s="98">
         <v>64</v>
       </c>
-      <c r="G3" s="82">
+      <c r="G3" s="100">
         <v>83.33</v>
       </c>
-      <c r="H3" s="84">
+      <c r="H3" s="102">
         <v>46.67</v>
       </c>
-      <c r="I3" s="86">
+      <c r="I3" s="104">
         <v>90.25</v>
       </c>
-      <c r="J3" s="88">
+      <c r="J3" s="106">
         <v>0</v>
       </c>
-      <c r="K3" s="90">
+      <c r="K3" s="108">
         <v>81.43</v>
       </c>
-      <c r="L3" s="92">
+      <c r="L3" s="110">
         <v>0</v>
       </c>
-      <c r="M3" s="94">
+      <c r="M3" s="112">
         <v>75.61</v>
       </c>
-      <c r="N3" s="96">
+      <c r="N3" s="114">
         <v>0</v>
       </c>
-      <c r="O3" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" s="100" t="inlineStr">
+      <c r="O3" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5349,42 +5716,42 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="78">
+      <c r="E4" s="96">
         <v>67.92</v>
       </c>
-      <c r="F4" s="80">
+      <c r="F4" s="98">
         <v>37.58</v>
       </c>
-      <c r="G4" s="82">
+      <c r="G4" s="100">
         <v>0</v>
       </c>
-      <c r="H4" s="84">
+      <c r="H4" s="102">
         <v>33.33</v>
       </c>
-      <c r="I4" s="86">
+      <c r="I4" s="104">
         <v>84.09</v>
       </c>
-      <c r="J4" s="88">
+      <c r="J4" s="106">
         <v>0</v>
       </c>
-      <c r="K4" s="90">
+      <c r="K4" s="108">
         <v>0</v>
       </c>
-      <c r="L4" s="92">
+      <c r="L4" s="110">
         <v>11.11</v>
       </c>
-      <c r="M4" s="94">
+      <c r="M4" s="112">
         <v>84</v>
       </c>
-      <c r="N4" s="96">
+      <c r="N4" s="114">
         <v>0</v>
       </c>
-      <c r="O4" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" s="100" t="inlineStr">
+      <c r="O4" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5409,40 +5776,40 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="78">
+      <c r="E5" s="96">
         <v>65.35</v>
       </c>
-      <c r="F5" s="80">
+      <c r="F5" s="98">
         <v>72.17</v>
       </c>
-      <c r="G5" s="82">
+      <c r="G5" s="100">
         <v>80.67</v>
       </c>
-      <c r="H5" s="84">
+      <c r="H5" s="102">
         <v>40</v>
       </c>
-      <c r="I5" s="86">
+      <c r="I5" s="104">
         <v>65.25</v>
       </c>
-      <c r="J5" s="88">
+      <c r="J5" s="106">
         <v>75</v>
       </c>
-      <c r="K5" s="90">
+      <c r="K5" s="108">
         <v>56</v>
       </c>
-      <c r="L5" s="92">
+      <c r="L5" s="110">
         <v>13.89</v>
       </c>
-      <c r="M5" s="94">
+      <c r="M5" s="112">
         <v>75.61</v>
       </c>
-      <c r="N5" s="96">
+      <c r="N5" s="114">
         <v>58.62</v>
       </c>
-      <c r="O5" s="98">
+      <c r="O5" s="116">
         <v>100</v>
       </c>
-      <c r="P5" s="100">
+      <c r="P5" s="118">
         <v>50</v>
       </c>
     </row>
@@ -5465,158 +5832,158 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="78">
+      <c r="E6" s="96">
         <v>63.52</v>
       </c>
-      <c r="F6" s="80">
+      <c r="F6" s="98">
         <v>58.42</v>
       </c>
-      <c r="G6" s="82">
+      <c r="G6" s="100">
         <v>0</v>
       </c>
-      <c r="H6" s="84">
+      <c r="H6" s="102">
         <v>38.89</v>
       </c>
-      <c r="I6" s="86">
+      <c r="I6" s="104">
         <v>83.33</v>
       </c>
-      <c r="J6" s="88">
+      <c r="J6" s="106">
         <v>0</v>
       </c>
-      <c r="K6" s="90">
+      <c r="K6" s="108">
         <v>52</v>
       </c>
-      <c r="L6" s="92">
+      <c r="L6" s="110">
         <v>25</v>
       </c>
-      <c r="M6" s="94">
+      <c r="M6" s="112">
         <v>94.67</v>
       </c>
-      <c r="N6" s="96">
+      <c r="N6" s="114">
         <v>17.24</v>
       </c>
-      <c r="O6" s="98">
+      <c r="O6" s="116">
         <v>55.33</v>
       </c>
-      <c r="P6" s="100" t="inlineStr">
+      <c r="P6" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA DEL RÍO GRANDE (por población 2024)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="79">
+      <c r="C7" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="97">
         <v>65.4544223983283</v>
       </c>
-      <c r="F7" s="81">
+      <c r="F7" s="99">
         <v>59.204534074556</v>
       </c>
-      <c r="G7" s="83">
+      <c r="G7" s="101">
         <v>35.466642123524</v>
       </c>
-      <c r="H7" s="85">
+      <c r="H7" s="103">
         <v>37.5929753385771</v>
       </c>
-      <c r="I7" s="87">
+      <c r="I7" s="105">
         <v>77.4515573560431</v>
       </c>
-      <c r="J7" s="89">
+      <c r="J7" s="107">
         <v>22.1612750606186</v>
       </c>
-      <c r="K7" s="91">
+      <c r="K7" s="109">
         <v>54.1683009048436</v>
       </c>
-      <c r="L7" s="93">
+      <c r="L7" s="111">
         <v>16.9774083821239</v>
       </c>
-      <c r="M7" s="95">
+      <c r="M7" s="113">
         <v>84.9792448794528</v>
       </c>
-      <c r="N7" s="97">
+      <c r="N7" s="115">
         <v>22.0245650245431</v>
       </c>
-      <c r="O7" s="99">
+      <c r="O7" s="117">
         <v>72.143928656969</v>
       </c>
-      <c r="P7" s="101">
+      <c r="P7" s="119">
         <v>50</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN NORTE (por población 2024)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="95" t="inlineStr">
         <is>
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="79">
+      <c r="D8" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="97">
         <v>62.1143595323915</v>
       </c>
-      <c r="F8" s="81">
+      <c r="F8" s="99">
         <v>60.679905786374</v>
       </c>
-      <c r="G8" s="83">
+      <c r="G8" s="101">
         <v>23.2966390435426</v>
       </c>
-      <c r="H8" s="85">
+      <c r="H8" s="103">
         <v>33.8909365445885</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="105">
         <v>48.5757102227014</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="107">
         <v>17.6279142261771</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="109">
         <v>44.0155392141087</v>
       </c>
-      <c r="L8" s="93">
+      <c r="L8" s="111">
         <v>19.998202257587</v>
       </c>
-      <c r="M8" s="95">
+      <c r="M8" s="113">
         <v>83.1339263991246</v>
       </c>
-      <c r="N8" s="97">
+      <c r="N8" s="115">
         <v>25.7734276944614</v>
       </c>
-      <c r="O8" s="99">
+      <c r="O8" s="117">
         <v>79.3092310976695</v>
       </c>
-      <c r="P8" s="101">
+      <c r="P8" s="119">
         <v>61.4050885752644</v>
       </c>
     </row>
@@ -5632,35 +5999,35 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="121" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="121" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="121" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="121" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="121" t="inlineStr">
         <is>
           <t>Tasa de tránsito inmediato a la educación superior</t>
         </is>
@@ -5685,7 +6052,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="102">
+      <c r="E2" s="123">
         <v>0.29</v>
       </c>
     </row>
@@ -5708,7 +6075,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="102">
+      <c r="E3" s="123">
         <v>0.22</v>
       </c>
     </row>
@@ -5731,7 +6098,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="102">
+      <c r="E4" s="123">
         <v>0.351351351351351</v>
       </c>
     </row>
@@ -5754,7 +6121,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="102">
+      <c r="E5" s="123">
         <v>0.311111111111111</v>
       </c>
     </row>
@@ -5777,32 +6144,32 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="102">
+      <c r="E6" s="123">
         <v>0.355339805825243</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="122" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="103">
+      <c r="C7" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="124">
         <v>0.305560453657541</v>
       </c>
     </row>
@@ -5818,53 +6185,53 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="58.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="80.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="59.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="126" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="126" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="126" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="126" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo por fibra óptica</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="126" t="inlineStr">
         <is>
           <t>Proporción de líneas sobre fibra óptica</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo por cada 1.000 habitantes</t>
         </is>
@@ -5889,17 +6256,17 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="104">
-        <v>3043</v>
-      </c>
-      <c r="F2" s="106">
-        <v>876</v>
-      </c>
-      <c r="G2" s="108">
-        <v>0.287873808741374</v>
-      </c>
-      <c r="H2" s="110">
-        <v>494.71630629166</v>
+      <c r="E2" s="128">
+        <v>951</v>
+      </c>
+      <c r="F2" s="130">
+        <v>324</v>
+      </c>
+      <c r="G2" s="132">
+        <v>0.340694006309148</v>
+      </c>
+      <c r="H2" s="134">
+        <v>154.609006665583</v>
       </c>
     </row>
     <row r="3">
@@ -5921,17 +6288,17 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="104">
-        <v>18427</v>
-      </c>
-      <c r="F3" s="106">
-        <v>17003</v>
-      </c>
-      <c r="G3" s="108">
-        <v>0.922722092581538</v>
-      </c>
-      <c r="H3" s="110">
-        <v>930.985702015864</v>
+      <c r="E3" s="128">
+        <v>4825</v>
+      </c>
+      <c r="F3" s="130">
+        <v>4368</v>
+      </c>
+      <c r="G3" s="132">
+        <v>0.905284974093264</v>
+      </c>
+      <c r="H3" s="134">
+        <v>243.773051078664</v>
       </c>
     </row>
     <row r="4">
@@ -5953,17 +6320,17 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="104">
-        <v>11187</v>
-      </c>
-      <c r="F4" s="106">
-        <v>6046</v>
-      </c>
-      <c r="G4" s="108">
-        <v>0.540448735139001</v>
-      </c>
-      <c r="H4" s="110">
-        <v>878.376256281407</v>
+      <c r="E4" s="128">
+        <v>2499</v>
+      </c>
+      <c r="F4" s="130">
+        <v>1269</v>
+      </c>
+      <c r="G4" s="132">
+        <v>0.507803121248499</v>
+      </c>
+      <c r="H4" s="134">
+        <v>196.215452261307</v>
       </c>
     </row>
     <row r="5">
@@ -5985,17 +6352,17 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="104">
-        <v>22452</v>
-      </c>
-      <c r="F5" s="106">
-        <v>7423</v>
-      </c>
-      <c r="G5" s="108">
-        <v>0.330616426153572</v>
-      </c>
-      <c r="H5" s="110">
-        <v>1007.40341903352</v>
+      <c r="E5" s="128">
+        <v>7347</v>
+      </c>
+      <c r="F5" s="130">
+        <v>5973</v>
+      </c>
+      <c r="G5" s="132">
+        <v>0.812984891792568</v>
+      </c>
+      <c r="H5" s="134">
+        <v>329.654058419707</v>
       </c>
     </row>
     <row r="6">
@@ -6017,51 +6384,51 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="104">
-        <v>13090</v>
-      </c>
-      <c r="F6" s="106">
-        <v>9474</v>
-      </c>
-      <c r="G6" s="108">
-        <v>0.72375859434683</v>
-      </c>
-      <c r="H6" s="110">
-        <v>325.128536300638</v>
+      <c r="E6" s="128">
+        <v>3595</v>
+      </c>
+      <c r="F6" s="130">
+        <v>2629</v>
+      </c>
+      <c r="G6" s="132">
+        <v>0.731293463143254</v>
+      </c>
+      <c r="H6" s="134">
+        <v>89.2923673033457</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="105">
-        <v>13639.8</v>
-      </c>
-      <c r="F7" s="107">
-        <v>8164.4</v>
-      </c>
-      <c r="G7" s="109">
-        <v>0.561083931392463</v>
-      </c>
-      <c r="H7" s="111">
-        <v>727.322043984617</v>
+      <c r="A7" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="127" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RÍO GRANDE (suma de líneas; razones recalculadas sobre las sumas)</t>
+        </is>
+      </c>
+      <c r="C7" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="129">
+        <v>19217</v>
+      </c>
+      <c r="F7" s="131">
+        <v>14563</v>
+      </c>
+      <c r="G7" s="133">
+        <v>0.757818598116251</v>
+      </c>
+      <c r="H7" s="135">
+        <v>189.838779784249</v>
       </c>
     </row>
   </sheetData>
